--- a/src/main/resources/templates/system/export/complete.xlsx
+++ b/src/main/resources/templates/system/export/complete.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HM\JAVA\DM\nitsm\src\main\resources\templates\system\export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tool\DM\nitsm_jinan\src\main\resources\templates\system\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329A3B04-4432-4FB2-9FFA-B1C44D5EF0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE912BF-EE8D-41F5-B860-A5E552F3A93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>机柜</t>
   </si>
@@ -285,6 +285,14 @@
   </si>
   <si>
     <t>是否为核心网络设备</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>serviceTypeId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -741,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="12" width="11" style="7" customWidth="1" collapsed="1"/>
@@ -751,22 +759,23 @@
     <col min="16" max="16" width="11" style="7" customWidth="1" collapsed="1"/>
     <col min="17" max="17" width="16.33203125" style="7" customWidth="1" collapsed="1"/>
     <col min="18" max="18" width="13.25" style="7" customWidth="1" collapsed="1"/>
-    <col min="19" max="24" width="11" style="7" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="13.25" style="7" customWidth="1" collapsed="1"/>
-    <col min="26" max="27" width="11" style="8" customWidth="1" collapsed="1"/>
-    <col min="28" max="32" width="11" style="7" customWidth="1" collapsed="1"/>
-    <col min="33" max="33" width="12.5" style="7" customWidth="1" collapsed="1"/>
-    <col min="34" max="34" width="11" style="8" customWidth="1" collapsed="1"/>
-    <col min="35" max="35" width="14.5" style="7" customWidth="1" collapsed="1"/>
-    <col min="36" max="36" width="15.1640625" style="7" customWidth="1" collapsed="1"/>
-    <col min="37" max="37" width="10.5" style="7" customWidth="1" collapsed="1"/>
-    <col min="38" max="41" width="11" style="7" customWidth="1" collapsed="1"/>
-    <col min="42" max="42" width="15.08203125" style="7" customWidth="1" collapsed="1"/>
-    <col min="43" max="43" width="15.83203125" style="7" customWidth="1" collapsed="1"/>
-    <col min="44" max="16384" width="8.6640625" style="7"/>
+    <col min="19" max="19" width="12.25" style="7" customWidth="1"/>
+    <col min="20" max="25" width="11" style="7" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="13.25" style="7" customWidth="1" collapsed="1"/>
+    <col min="27" max="28" width="11" style="8" customWidth="1" collapsed="1"/>
+    <col min="29" max="33" width="11" style="7" customWidth="1" collapsed="1"/>
+    <col min="34" max="34" width="12.5" style="7" customWidth="1" collapsed="1"/>
+    <col min="35" max="35" width="11" style="8" customWidth="1" collapsed="1"/>
+    <col min="36" max="36" width="14.5" style="7" customWidth="1" collapsed="1"/>
+    <col min="37" max="37" width="15.1640625" style="7" customWidth="1" collapsed="1"/>
+    <col min="38" max="38" width="10.5" style="7" customWidth="1" collapsed="1"/>
+    <col min="39" max="42" width="11" style="7" customWidth="1" collapsed="1"/>
+    <col min="43" max="43" width="15.08203125" style="7" customWidth="1" collapsed="1"/>
+    <col min="44" max="44" width="15.83203125" style="7" customWidth="1" collapsed="1"/>
+    <col min="45" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>77</v>
       </c>
@@ -822,82 +831,85 @@
         <v>83</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -953,78 +965,81 @@
         <v>52</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AA2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AB2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AI2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1038,22 +1053,21 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="安全边界/PDU等类型无需填写ip地址" prompt=" " sqref="J1" xr:uid="{E9FF10D0-E8E9-4455-AC8A-2136CF0AE41C}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="安全边界/PDU等类型无需填写ip" sqref="J3:J5" xr:uid="{8DD76370-C485-4455-A707-948417357905}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="*必填" prompt=" " sqref="A1:F1" xr:uid="{D8D135C1-6086-4EC7-8E45-34160A7A85A5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可为空" prompt=" " sqref="X1" xr:uid="{34399B35-0F8D-4982-8DC1-B2F32662E15F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="可为空" sqref="X3:X5" xr:uid="{556EC9E8-6C2D-4933-90B7-AD1994B22760}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可为空" prompt=" " sqref="Y1" xr:uid="{34399B35-0F8D-4982-8DC1-B2F32662E15F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="可为空" sqref="Y3:Y5" xr:uid="{556EC9E8-6C2D-4933-90B7-AD1994B22760}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="必填" prompt=" " sqref="K1" xr:uid="{B4EDE4FD-F779-4330-9502-8E386B0056A7}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="必填" sqref="K3:K5" xr:uid="{5A62C7E7-BCAC-4B1C-A809-8CF21E1B596B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="必填" sqref="K3:K5 A3:F3 A5:F5 A4 C4:F4" xr:uid="{5A62C7E7-BCAC-4B1C-A809-8CF21E1B596B}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="是否为需要监控设备(会验证采集相关信息)" prompt=" " sqref="L1" xr:uid="{52ACE6EB-96D8-42B5-AE9B-981433FFC031}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="是否需要在前台topo图上显示" prompt=" " sqref="M1" xr:uid="{2AA0C85B-1297-43BB-B0BC-917DFC604347}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可空" prompt="默认为否" sqref="O3:O5 L3:M5" xr:uid="{4C64CA98-A193-49C0-AFA6-22516186B456}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="监控时是否需采集系统时间" prompt=" " sqref="O1" xr:uid="{70E10BAC-435D-4A38-AE59-0DA97B725C9F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="服务器/工控机/终端" prompt="以上设备:windows采集类型时,需填写登录密码" sqref="R2:R5" xr:uid="{487C3487-4FF1-4BD8-8043-9E41C999A578}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="A机/B机" prompt=" " sqref="W1:X1" xr:uid="{2498C874-F66B-4242-918F-4E01C99F4E7B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A机/B机" sqref="W3:X5" xr:uid="{B3441FD0-A4BA-4432-A98D-C3BD7A48AE82}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="格式样例: 2021-06-13 15:06:00" prompt=" " sqref="AH1:AH5 Z1:AA5" xr:uid="{C4CDF2A9-8230-4A43-9A37-AB7DF9323AC0}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写整数" sqref="AL1" xr:uid="{A5FF6A90-176F-4E4E-B86A-565EB0016D20}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写整数" prompt=" " sqref="V1 AE1 AC1 AI1" xr:uid="{0287C144-D021-4370-AE06-95DAB1C8E3D9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写: 单机部署/:双机热备" prompt=" " sqref="AG1:AG5" xr:uid="{AAB2AF13-F157-4F8E-910F-94592721F577}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="必填" sqref="A3:F3 A5:F5 A4 C4:F4" xr:uid="{F625118F-3FC5-4197-938F-16071F77464E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="A机/B机" prompt=" " sqref="X1:Y1" xr:uid="{2498C874-F66B-4242-918F-4E01C99F4E7B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A机/B机" sqref="X3:Y5" xr:uid="{B3441FD0-A4BA-4432-A98D-C3BD7A48AE82}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="格式样例: 2021-06-13 15:06:00" prompt=" " sqref="AI1:AI5 AA1:AB5" xr:uid="{C4CDF2A9-8230-4A43-9A37-AB7DF9323AC0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写整数" sqref="AM1" xr:uid="{A5FF6A90-176F-4E4E-B86A-565EB0016D20}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写整数" prompt=" " sqref="W1 AF1 AD1 AJ1" xr:uid="{0287C144-D021-4370-AE06-95DAB1C8E3D9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请填写: 单机部署/:双机热备" prompt=" " sqref="AH1:AH5" xr:uid="{AAB2AF13-F157-4F8E-910F-94592721F577}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="交换机/路由器" prompt="如需设置为核心交换机或核心路由器可填写" sqref="N1" xr:uid="{DC11F3C3-979D-40F5-8030-D0EB097E3E59}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可空" prompt="默认为普通网络设备" sqref="N3:N5" xr:uid="{2538B52D-F55F-45E8-9A09-3B98A6DF5657}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="服务器/工控机/终端_x000a_以上设备:windows采集类型时,需填写登录密码" sqref="R1" xr:uid="{AB30267D-6F98-475A-B8F9-C2F6F20E3BFA}"/>
@@ -1061,6 +1075,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="采集类型&gt;windows(填团体名称)_x000a_其余采集类型&gt;(用户名+密码)" sqref="Q1" xr:uid="{04980DE4-31F5-4A80-8851-6A2013CCD641}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="linux/windows/aix" prompt=" 不监控无需填写" sqref="P3:P5" xr:uid="{57483C4E-176E-4FC8-9848-A3527ED48872}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="监控服务器/工控机/终端时 :需填写" prompt="不监控时无需填写" sqref="P1" xr:uid="{CA4E2014-C2BE-4A49-8C49-0C0489763996}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="仅业务相关设备需填写" prompt="应用服务器_x000a_TDMS接口服务器_x000a_TSRS接口服务器_x000a_COMSERVER_x000a_自律机_x000a_TD接口服务器_x000a_调度台_x000a_调度命令_x000a_报部接口服务器_x000a_通信前置机" sqref="S1" xr:uid="{62BAD8E8-2762-4EFE-8B0D-11D200F773CB}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/system/export/complete.xlsx
+++ b/src/main/resources/templates/system/export/complete.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tool\DM\nitsm_jinan\src\main\resources\templates\system\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE912BF-EE8D-41F5-B860-A5E552F3A93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC2E85E-46C9-494A-B851-9BFAED721630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations xWindow="497" yWindow="431" count="30">
+  <dataValidations xWindow="497" yWindow="431" count="29">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="终端可为空" prompt=" " sqref="G1" xr:uid="{C9199D6D-342C-4063-A819-A170AEE39906}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="除终端设备外,皆需填写机柜及位置信息" sqref="G3:G5" xr:uid="{F9CBDB85-3314-4E66-B05B-1D773C5A0C8D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="终端可为空" prompt="0~42" sqref="H1:I1" xr:uid="{A946CC27-1FDD-4641-B07F-724F66573938}"/>
@@ -1073,7 +1073,6 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="服务器/工控机/终端_x000a_以上设备:windows采集类型时,需填写登录密码" sqref="R1" xr:uid="{AB30267D-6F98-475A-B8F9-C2F6F20E3BFA}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控无需填写" prompt="小型机-&gt;用户名密码_x000a_交换机/路由器-&gt;团体名" sqref="Q3:Q5" xr:uid="{0651B2B8-8030-4B73-974F-DF901E3D796F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="采集类型&gt;windows(填团体名称)_x000a_其余采集类型&gt;(用户名+密码)" sqref="Q1" xr:uid="{04980DE4-31F5-4A80-8851-6A2013CCD641}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="linux/windows/aix" prompt=" 不监控无需填写" sqref="P3:P5" xr:uid="{57483C4E-176E-4FC8-9848-A3527ED48872}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="监控服务器/工控机/终端时 :需填写" prompt="不监控时无需填写" sqref="P1" xr:uid="{CA4E2014-C2BE-4A49-8C49-0C0489763996}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="仅业务相关设备需填写" prompt="应用服务器_x000a_TDMS接口服务器_x000a_TSRS接口服务器_x000a_COMSERVER_x000a_自律机_x000a_TD接口服务器_x000a_调度台_x000a_调度命令_x000a_报部接口服务器_x000a_通信前置机" sqref="S1" xr:uid="{62BAD8E8-2762-4EFE-8B0D-11D200F773CB}"/>
   </dataValidations>
